--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>/Game/Commander/Units/SM_CommanderFourFRobot.SM_CommanderFourFRobot</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/SM_CommanderFourFRobot_Crowd.SM_CommanderFourFRobot_Crowd</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>0</v>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -4,17 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Soldiers" sheetId="2" r:id="rId4"/>
+    <sheet name="Skills" sheetId="3" r:id="rId6"/>
+    <sheet name="UnitSkills" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>id</t>
   </si>
@@ -71,6 +73,102 @@
   </si>
   <si>
     <t>/Game/Commander/Units/SM_CommanderFourFRobot_Crowd.SM_CommanderFourFRobot_Crowd</t>
+  </si>
+  <si>
+    <t>扫射调试兵种A；数值非平衡定案</t>
+  </si>
+  <si>
+    <t>TestSoldierB</t>
+  </si>
+  <si>
+    <t>扫射调试兵种B；浮点生命和多兵种验证</t>
+  </si>
+  <si>
+    <t>SkillId</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>ExecutorId</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>Strafe</t>
+  </si>
+  <si>
+    <t>单体直接伤害；不接视觉表现</t>
+  </si>
+  <si>
+    <t>扫射</t>
+  </si>
+  <si>
+    <t>DirectSingleTarget</t>
+  </si>
+  <si>
+    <t>Skill.Attack.Basic;Skill.Usage.Common;Weapon.MachineGun</t>
+  </si>
+  <si>
+    <t>StrafeTest</t>
+  </si>
+  <si>
+    <t>替换接口测试；不是正式火炮</t>
+  </si>
+  <si>
+    <t>扫射测试变体</t>
+  </si>
+  <si>
+    <t>Skill.Attack.Basic;Skill.Usage.Common;Weapon.Test</t>
+  </si>
+  <si>
+    <t>UnitTypeId</t>
+  </si>
+  <si>
+    <t>SlotId</t>
+  </si>
+  <si>
+    <t>bDefault</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>AttackRatePerSecond</t>
+  </si>
+  <si>
+    <t>RangeCentimeters</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>SoldierA_Strafe</t>
+  </si>
+  <si>
+    <t>A默认普攻</t>
+  </si>
+  <si>
+    <t>BasicAttack</t>
+  </si>
+  <si>
+    <t>SoldierB_Strafe</t>
+  </si>
+  <si>
+    <t>B默认普攻</t>
+  </si>
+  <si>
+    <t>SoldierA_Test</t>
+  </si>
+  <si>
+    <t>A替换验证</t>
+  </si>
+  <si>
+    <t>SoldierB_Test</t>
+  </si>
+  <si>
+    <t>B替换验证</t>
   </si>
 </sst>
 </file>
@@ -406,7 +504,7 @@
     <col customWidth="true" max="1" min="1" width="10"/>
     <col customWidth="true" max="2" min="2" width="22"/>
     <col customWidth="true" max="3" min="3" width="46"/>
-    <col customWidth="true" max="9" min="4" width="28"/>
+    <col customWidth="true" max="7" min="4" width="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -429,13 +527,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -452,7 +544,7 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -460,12 +552,270 @@
       <c r="G2" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>3600</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>3600</v>
+      </c>
+      <c r="E5">
+        <v>300.5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>41</v>
+      </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
       </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -495,34 +845,136 @@
       <c r="I3" t="s">
         <v>13</v>
       </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>7.5</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>3600</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Soldiers" sheetId="2" r:id="rId4"/>
     <sheet name="Skills" sheetId="3" r:id="rId6"/>
     <sheet name="UnitSkills" sheetId="4" r:id="rId7"/>
+    <sheet name="SpellFields" sheetId="5" r:id="rId8"/>
+    <sheet name="WeaponMounts" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -169,6 +171,165 @@
   </si>
   <si>
     <t>B替换验证</t>
+  </si>
+  <si>
+    <t>WM01</t>
+  </si>
+  <si>
+    <t>WM01 第二兵种；首版沿用调试数值，尚未平衡</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/SM_WM01_Crowd.SM_WM01_Crowd</t>
+  </si>
+  <si>
+    <t>WM01_Strafe</t>
+  </si>
+  <si>
+    <t>WM01 默认普攻</t>
+  </si>
+  <si>
+    <t>WM01_Test</t>
+  </si>
+  <si>
+    <t>WM01 替换验证</t>
+  </si>
+  <si>
+    <t>机枪即时单体伤害与枪火表现</t>
+  </si>
+  <si>
+    <t>WM01_HomingMissile</t>
+  </si>
+  <si>
+    <t>独立自动导弹；爆炸由独立法术场结算；调试初值</t>
+  </si>
+  <si>
+    <t>WM01导弹</t>
+  </si>
+  <si>
+    <t>LaunchProjectile</t>
+  </si>
+  <si>
+    <t>Skill.Attack.Basic;Skill.Usage.Common;Weapon.Missile</t>
+  </si>
+  <si>
+    <t>WM01_MissileLauncher</t>
+  </si>
+  <si>
+    <t>默认解锁；3秒/枚，30伤害，150米射程；调试初值非最终平衡</t>
+  </si>
+  <si>
+    <t>MissileLauncher</t>
+  </si>
+  <si>
+    <t>EffectConfigId</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>WM01_MissileExplosion</t>
+  </si>
+  <si>
+    <t>默认解锁；3秒/枚，伤害由SpellFields表提供，150米射程；调试初值非最终平衡</t>
+  </si>
+  <si>
+    <t>RadiusCentimeters</t>
+  </si>
+  <si>
+    <t>Timing</t>
+  </si>
+  <si>
+    <t>DelaySeconds</t>
+  </si>
+  <si>
+    <t>DurationSeconds</t>
+  </si>
+  <si>
+    <t>PulseIntervalSeconds</t>
+  </si>
+  <si>
+    <t>DissipationSeconds</t>
+  </si>
+  <si>
+    <t>WM01导弹命中后的即时球形法术场；伤害、范围和时序均在本行配置</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>PointRole</t>
+  </si>
+  <si>
+    <t>PointIndex</t>
+  </si>
+  <si>
+    <t>SocketName</t>
+  </si>
+  <si>
+    <t>OffsetX</t>
+  </si>
+  <si>
+    <t>OffsetY</t>
+  </si>
+  <si>
+    <t>OffsetZ</t>
+  </si>
+  <si>
+    <t>bCalibrated</t>
+  </si>
+  <si>
+    <t>FourFRobot_AimTarget</t>
+  </si>
+  <si>
+    <t>FourFRobot 被攻击时的视觉瞄准点；来自 FX_AimTarget</t>
+  </si>
+  <si>
+    <t>AimTarget</t>
+  </si>
+  <si>
+    <t>FX_AimTarget</t>
+  </si>
+  <si>
+    <t>FourFRobot_BasicAttack_Muzzle_0</t>
+  </si>
+  <si>
+    <t>FourFRobot 机枪枪口；来自 FX_Muzzle_Basic_01</t>
+  </si>
+  <si>
+    <t>Muzzle</t>
+  </si>
+  <si>
+    <t>FX_Muzzle_Basic_01</t>
+  </si>
+  <si>
+    <t>WM01_AimTarget</t>
+  </si>
+  <si>
+    <t>WM01 被攻击时的视觉瞄准点；来自 FX_AimTarget</t>
+  </si>
+  <si>
+    <t>WM01_BasicAttack_Muzzle_0</t>
+  </si>
+  <si>
+    <t>WM01 前机枪枪口；来自 FX_Muzzle_Basic_01</t>
+  </si>
+  <si>
+    <t>WM01_MissileLauncher_Muzzle_0</t>
+  </si>
+  <si>
+    <t>WM01 导弹发射口 1；来自 FX_Missile_01</t>
+  </si>
+  <si>
+    <t>FX_Missile_01</t>
+  </si>
+  <si>
+    <t>WM01_MissileLauncher_Muzzle_1</t>
+  </si>
+  <si>
+    <t>WM01 导弹发射口 2；来自 FX_Missile_02</t>
+  </si>
+  <si>
+    <t>FX_Missile_02</t>
   </si>
 </sst>
 </file>
@@ -188,7 +349,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,6 +359,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -227,10 +403,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -604,10 +798,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>3600</v>
@@ -616,7 +810,7 @@
         <v>300.5</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -652,6 +846,9 @@
       <c r="G1" t="s">
         <v>25</v>
       </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -675,6 +872,9 @@
       <c r="G2" t="s">
         <v>10</v>
       </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -698,6 +898,9 @@
       <c r="G3" t="s">
         <v>13</v>
       </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -707,7 +910,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
@@ -720,6 +923,9 @@
       </c>
       <c r="G4" t="s">
         <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -743,6 +949,35 @@
       </c>
       <c r="G5" t="s">
         <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -886,10 +1121,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -950,10 +1185,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -975,6 +1210,536 @@
       </c>
       <c r="J7">
         <v>18000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J8">
+        <v>15000</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="2" min="2" width="28"/>
+    <col customWidth="true" max="3" min="3" width="56"/>
+    <col customWidth="true" max="10" min="4" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="4">
+        <v>30</v>
+      </c>
+      <c r="E4" s="4">
+        <v>800</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="8"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="3" min="3" width="48"/>
+    <col customWidth="true" max="4" min="4" width="12"/>
+    <col customWidth="true" max="5" min="5" width="20"/>
+    <col customWidth="true" max="6" min="6" width="14"/>
+    <col customWidth="true" max="7" min="7" width="12"/>
+    <col customWidth="true" max="8" min="8" width="28"/>
+    <col customWidth="true" max="12" min="9" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>650</v>
+      </c>
+      <c r="L4" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="7">
+        <v>-480</v>
+      </c>
+      <c r="J5" s="7">
+        <v>5</v>
+      </c>
+      <c r="K5" s="7">
+        <v>935</v>
+      </c>
+      <c r="L5" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>495</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1600</v>
+      </c>
+      <c r="L6" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1490</v>
+      </c>
+      <c r="J7" s="7">
+        <v>466</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1810</v>
+      </c>
+      <c r="L7" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="7">
+        <v>-260</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1257</v>
+      </c>
+      <c r="K8" s="7">
+        <v>2440</v>
+      </c>
+      <c r="L8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="7">
+        <v>-260</v>
+      </c>
+      <c r="J9" s="7">
+        <v>-326</v>
+      </c>
+      <c r="K9" s="7">
+        <v>2440</v>
+      </c>
+      <c r="L9" s="7" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>id</t>
   </si>
@@ -395,6 +395,18 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Vehicles/ElectromagneticMiner/BP_MiningVehicle_TransporterLvl2.BP_MiningVehicle_TransporterLvl2_C</t>
+  </si>
+  <si>
+    <t>ConstructionVehicle</t>
+  </si>
+  <si>
+    <t>开局每队一辆；独立建造车，施工与采矿分工</t>
+  </si>
+  <si>
+    <t>/Script/GuLiStrike.GuLiConstructionVehiclePawn</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Vehicles/ConstructionVehicle/BP_ConstructionVehicle.BP_ConstructionVehicle_C</t>
   </si>
 </sst>
 </file>
@@ -958,6 +970,38 @@
         <v>3.0422898572084356</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7">
+        <v>4500</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J7">
+        <v>3.0422898572084356</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>id</t>
   </si>
@@ -407,6 +407,24 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Vehicles/ConstructionVehicle/BP_ConstructionVehicle.BP_ConstructionVehicle_C</t>
+  </si>
+  <si>
+    <t>扫荡者</t>
+  </si>
+  <si>
+    <t>战争机器</t>
+  </si>
+  <si>
+    <t>电磁矿车</t>
+  </si>
+  <si>
+    <t>建造车</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/Tactical/Cel/Sweeper/Meshes/SM_Sweeper_Cel.SM_Sweeper_Cel</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/Tactical/Cel/WarMachine/Meshes/SM_WarMachine_Cel.SM_WarMachine_Cel</t>
   </si>
 </sst>
 </file>
@@ -809,6 +827,9 @@
       <c r="J1" t="s">
         <v>121</v>
       </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -841,6 +862,9 @@
       <c r="J2" t="s">
         <v>11</v>
       </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -873,6 +897,9 @@
       <c r="J3" t="s">
         <v>13</v>
       </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -891,7 +918,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -904,6 +931,9 @@
       </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5">
@@ -923,7 +953,7 @@
         <v>300.5</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -936,6 +966,9 @@
       </c>
       <c r="J5">
         <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -969,6 +1002,9 @@
       <c r="J6">
         <v>3.0422898572084356</v>
       </c>
+      <c r="K6" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1001,6 +1037,9 @@
       <c r="J7">
         <v>3.0422898572084356</v>
       </c>
+      <c r="K7" t="s">
+        <v>134</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -425,6 +425,9 @@
   </si>
   <si>
     <t>/Game/Commander/Units/Tactical/Cel/WarMachine/Meshes/SM_WarMachine_Cel.SM_WarMachine_Cel</t>
+  </si>
+  <si>
+    <t>指挥官可控制矿车；Scale020后车长3.6米，900cm/s；采矿业务由矿车Manager调度</t>
   </si>
 </sst>
 </file>
@@ -912,7 +915,7 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -930,7 +933,7 @@
         <v>68</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K4" t="s">
         <v>131</v>
@@ -947,7 +950,7 @@
         <v>52</v>
       </c>
       <c r="D5">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="E5">
         <v>300.5</v>
@@ -965,7 +968,7 @@
         <v>68</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="K5" t="s">
         <v>132</v>
@@ -979,10 +982,10 @@
         <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="D6">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="E6">
         <v>1000</v>
@@ -1000,7 +1003,7 @@
         <v>126</v>
       </c>
       <c r="J6">
-        <v>3.0422898572084356</v>
+        <v>0.6084579714416871</v>
       </c>
       <c r="K6" t="s">
         <v>133</v>
@@ -1017,7 +1020,7 @@
         <v>128</v>
       </c>
       <c r="D7">
-        <v>4500</v>
+        <v>900</v>
       </c>
       <c r="E7">
         <v>1000</v>
@@ -1035,7 +1038,7 @@
         <v>130</v>
       </c>
       <c r="J7">
-        <v>3.0422898572084356</v>
+        <v>0.6084579714416871</v>
       </c>
       <c r="K7" t="s">
         <v>134</v>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -13,8 +13,28 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>GuLiStrike</author>
+  </authors>
+  <commentList>
+    <comment ref="L1" authorId="0">
+      <text>
+        <t>模型宽度，单位：米。最终游戏尺度下用于平面圆形占地的直径。代码接入时半径=宽度×50厘米，不再乘PresentationScale，也不修改模型缩放。战争机器12.5米由用户指定；扫荡者按实测水平尺寸向上取3.1米；两种工程车按当前3.6米车长取值。</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0">
+      <text>
+        <t>最小避障距离，单位：米。两个单位圆形占地外缘之间的最小净距，不是中心距离。双方取较大值，不相加。最小中心距=(A模型宽度+B模型宽度)/2+max(A最小避障距离,B最小避障距离)。战争机器之间为15米。本次仅完成源表配置，运行时代码尚待接入。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -428,12 +448,21 @@
   </si>
   <si>
     <t>指挥官可控制矿车；Scale020后车长3.6米，900cm/s；采矿业务由矿车Manager调度</t>
+  </si>
+  <si>
+    <t>ModelWidthMeters</t>
+  </si>
+  <si>
+    <t>MinAvoidanceDistanceMeters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot; m&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -501,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -523,6 +552,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
+      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -790,13 +822,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="10"/>
     <col customWidth="true" max="2" min="2" width="22"/>
     <col customWidth="true" max="3" min="3" width="46"/>
     <col customWidth="true" max="7" min="4" width="28"/>
+    <col customWidth="true" max="12" min="12" width="26"/>
+    <col customWidth="true" max="13" min="13" width="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,6 +867,12 @@
       <c r="K1" t="s">
         <v>23</v>
       </c>
+      <c r="L1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M1" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -868,6 +908,12 @@
       <c r="K2" t="s">
         <v>10</v>
       </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -903,6 +949,12 @@
       <c r="K3" t="s">
         <v>14</v>
       </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -938,6 +990,12 @@
       <c r="K4" t="s">
         <v>131</v>
       </c>
+      <c r="L4" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -973,6 +1031,12 @@
       <c r="K5" t="s">
         <v>132</v>
       </c>
+      <c r="L5" s="8">
+        <v>12.5</v>
+      </c>
+      <c r="M5" s="8">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1008,6 +1072,12 @@
       <c r="K6" t="s">
         <v>133</v>
       </c>
+      <c r="L6" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1043,7 +1113,14 @@
       <c r="K7" t="s">
         <v>134</v>
       </c>
+      <c r="L7" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -454,6 +454,18 @@
   </si>
   <si>
     <t>MinAvoidanceDistanceMeters</t>
+  </si>
+  <si>
+    <t>StateTreeAsset</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Behavior/ST_CommanderMass.ST_CommanderMass</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Behavior/ST_CommanderMiner.ST_CommanderMiner</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Behavior/ST_CommanderBuilder.ST_CommanderBuilder</t>
   </si>
 </sst>
 </file>
@@ -831,6 +843,7 @@
     <col customWidth="true" max="7" min="4" width="28"/>
     <col customWidth="true" max="12" min="12" width="26"/>
     <col customWidth="true" max="13" min="13" width="35"/>
+    <col customWidth="true" max="14" min="14" width="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,6 +886,9 @@
       <c r="M1" t="s">
         <v>139</v>
       </c>
+      <c r="N1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -914,6 +930,9 @@
       <c r="M2" t="s">
         <v>11</v>
       </c>
+      <c r="N2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -955,6 +974,9 @@
       <c r="M3" t="s">
         <v>13</v>
       </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -996,6 +1018,9 @@
       <c r="M4" s="8">
         <v>0.5</v>
       </c>
+      <c r="N4" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -1037,6 +1062,9 @@
       <c r="M5" s="8">
         <v>2.5</v>
       </c>
+      <c r="N5" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1078,6 +1106,9 @@
       <c r="M6" s="8">
         <v>1</v>
       </c>
+      <c r="N6" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1118,6 +1149,9 @@
       </c>
       <c r="M7" s="8">
         <v>1</v>
+      </c>
+      <c r="N7" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -466,6 +466,15 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Commander/Behavior/ST_CommanderBuilder.ST_CommanderBuilder</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/Tactical/Cel/Sweeper/Meshes/SM_Sweeper_Rigid.SM_Sweeper_Rigid</t>
+  </si>
+  <si>
+    <t>/Game/Commander/Units/Tactical/Cel/WarMachine/Meshes/SM_WarMachine_Rigid.SM_WarMachine_Rigid</t>
+  </si>
+  <si>
+    <t>重防号</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1004,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1039,7 +1048,7 @@
         <v>300.5</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1054,7 +1063,7 @@
         <v>0.2</v>
       </c>
       <c r="K5" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L5" s="8">
         <v>12.5</v>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Soldiers" sheetId="2" r:id="rId4"/>
+    <sheet name="Camera" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>id</t>
   </si>
@@ -475,6 +476,129 @@
   </si>
   <si>
     <t>重防号</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>三档镜头；距离米、俯角向下为正、时间秒。x由战场和HUD可用画面计算；数值修改后导出并导入Camera表。</t>
+  </si>
+  <si>
+    <t>MinimumHeightMeters</t>
+  </si>
+  <si>
+    <t>TacticalStartHeightMeters</t>
+  </si>
+  <si>
+    <t>TacticalMaximumHeightMeters</t>
+  </si>
+  <si>
+    <t>InitialHeightMeters</t>
+  </si>
+  <si>
+    <t>NearPitchDegrees</t>
+  </si>
+  <si>
+    <t>TacticalPitchDegrees</t>
+  </si>
+  <si>
+    <t>OverviewPitchDegrees</t>
+  </si>
+  <si>
+    <t>FieldOfViewDegrees</t>
+  </si>
+  <si>
+    <t>ZoomStepMultiplier</t>
+  </si>
+  <si>
+    <t>ZoomInterpolationSpeed</t>
+  </si>
+  <si>
+    <t>YawDegreesPerSecond</t>
+  </si>
+  <si>
+    <t>MoveHeightMultiplier</t>
+  </si>
+  <si>
+    <t>MinimumMoveMetersPerSecond</t>
+  </si>
+  <si>
+    <t>MaximumMoveMetersPerSecond</t>
+  </si>
+  <si>
+    <t>RiseHalfLifeSeconds</t>
+  </si>
+  <si>
+    <t>DescentHalfLifeSeconds</t>
+  </si>
+  <si>
+    <t>MaximumRiseMetersPerSecond</t>
+  </si>
+  <si>
+    <t>MaximumDescentMetersPerSecond</t>
+  </si>
+  <si>
+    <t>LookAheadSeconds</t>
+  </si>
+  <si>
+    <t>BoundaryPaddingMeters</t>
+  </si>
+  <si>
+    <t>PivotClearanceMeters</t>
+  </si>
+  <si>
+    <t>BoomClearanceMeters</t>
+  </si>
+  <si>
+    <t>CameraClearanceMeters</t>
+  </si>
+  <si>
+    <t>BoomSampleSpacingMeters</t>
+  </si>
+  <si>
+    <t>OverviewTransitionSeconds</t>
+  </si>
+  <si>
+    <t>OverviewPaddingFraction</t>
+  </si>
+  <si>
+    <t>OverviewUnitIconPixels</t>
+  </si>
+  <si>
+    <t>OverviewBuildingIconPixels</t>
+  </si>
+  <si>
+    <t>ZoomInterpolationPerSecond</t>
+  </si>
+  <si>
+    <t>MoveHeightMultiplierPerSecond</t>
+  </si>
+  <si>
+    <t>OverviewYawDegrees</t>
+  </si>
+  <si>
+    <t>VATDefinition</t>
+  </si>
+  <si>
+    <t>bSummonOnly</t>
+  </si>
+  <si>
+    <t>B-v1先驱号；6.25米；刚性骨骼纹理VAT；默认双枪与Q召唤</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Robots/RSGMech/Meshes/SM_Pioneer_VAT.SM_Pioneer_VAT</t>
+  </si>
+  <si>
+    <t>先驱号</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Robots/RSGMech/VAT/DA_Pioneer_VAT.DA_Pioneer_VAT</t>
+  </si>
+  <si>
+    <t>SweeperSummon</t>
+  </si>
+  <si>
+    <t>先驱号Q专用召唤兵；永久可控、可累积、不计生产人口</t>
   </si>
 </sst>
 </file>
@@ -551,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -576,6 +700,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
       <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -898,6 +1028,12 @@
       <c r="N1" t="s">
         <v>140</v>
       </c>
+      <c r="O1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -942,6 +1078,12 @@
       <c r="N2" t="s">
         <v>12</v>
       </c>
+      <c r="O2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -985,6 +1127,12 @@
       </c>
       <c r="N3" t="s">
         <v>13</v>
+      </c>
+      <c r="O3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +1143,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>182</v>
       </c>
       <c r="D4">
-        <v>720</v>
+        <v>1440</v>
       </c>
       <c r="E4">
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1016,19 +1164,25 @@
         <v>68</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="L4" s="8">
-        <v>3.1</v>
+        <v>6.25</v>
       </c>
       <c r="M4" s="8">
         <v>0.5</v>
       </c>
       <c r="N4" t="s">
         <v>141</v>
+      </c>
+      <c r="O4" t="s">
+        <v>185</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1074,6 +1228,9 @@
       <c r="N5" t="s">
         <v>141</v>
       </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -1118,6 +1275,9 @@
       <c r="N6" t="s">
         <v>142</v>
       </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -1162,8 +1322,456 @@
       <c r="N7" t="s">
         <v>143</v>
       </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8">
+        <v>720</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.2</v>
+      </c>
+      <c r="K8" t="s">
+        <v>131</v>
+      </c>
+      <c r="L8">
+        <v>3.1</v>
+      </c>
+      <c r="M8">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="s">
+        <v>141</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="3" min="3" width="55"/>
+    <col customWidth="true" max="32" min="4" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="true">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="P1" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="V1" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="X1" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z1" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA1" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB1" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="AC1" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="AD1" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="AE1" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF1" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V2" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" t="s">
+        <v>11</v>
+      </c>
+      <c r="X2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" t="s">
+        <v>13</v>
+      </c>
+      <c r="S3" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V3" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="true">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <v>300</v>
+      </c>
+      <c r="F4">
+        <v>700</v>
+      </c>
+      <c r="G4">
+        <v>133.4</v>
+      </c>
+      <c r="H4">
+        <v>25</v>
+      </c>
+      <c r="I4">
+        <v>55</v>
+      </c>
+      <c r="J4">
+        <v>90</v>
+      </c>
+      <c r="K4">
+        <v>45</v>
+      </c>
+      <c r="L4">
+        <v>1.18</v>
+      </c>
+      <c r="M4">
+        <v>8</v>
+      </c>
+      <c r="N4">
+        <v>70</v>
+      </c>
+      <c r="O4">
+        <v>1.4</v>
+      </c>
+      <c r="P4">
+        <v>12</v>
+      </c>
+      <c r="Q4">
+        <v>92</v>
+      </c>
+      <c r="R4">
+        <v>0.2</v>
+      </c>
+      <c r="S4">
+        <v>0.35</v>
+      </c>
+      <c r="T4">
+        <v>60</v>
+      </c>
+      <c r="U4">
+        <v>30</v>
+      </c>
+      <c r="V4">
+        <v>0.75</v>
+      </c>
+      <c r="W4">
+        <v>10</v>
+      </c>
+      <c r="X4">
+        <v>0.3</v>
+      </c>
+      <c r="Y4">
+        <v>0.4</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>20</v>
+      </c>
+      <c r="AB4">
+        <v>0.6</v>
+      </c>
+      <c r="AC4">
+        <v>0.05</v>
+      </c>
+      <c r="AD4">
+        <v>14</v>
+      </c>
+      <c r="AE4">
+        <v>20</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>id</t>
   </si>
@@ -599,6 +599,54 @@
   </si>
   <si>
     <t>先驱号Q专用召唤兵；永久可控、可累积、不计生产人口</t>
+  </si>
+  <si>
+    <t>bConstructionOnly</t>
+  </si>
+  <si>
+    <t>FacingPolicy</t>
+  </si>
+  <si>
+    <t>MassAvoidanceRadiusMeters</t>
+  </si>
+  <si>
+    <t>BiZhiMao</t>
+  </si>
+  <si>
+    <t>工程车施工生成；底座锁定出生朝向；首轮不攻击；已审ControlRig B_v4放大2倍</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/BiZhiMao/Meshes/SM_BiZhiMao_VAT.SM_BiZhiMao_VAT</t>
+  </si>
+  <si>
+    <t>彼之矛</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/BiZhiMao/VAT/DA_BiZhiMao_VAT.DA_BiZhiMao_VAT</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/DefaultSoldier/LOD_3Tier_v1/Meshes/SM_Pioneer_VAT.SM_Pioneer_VAT</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/DefaultSoldier/LOD_3Tier_v1/VAT/DA_Pioneer_VAT.DA_Pioneer_VAT</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/WM01/LOD_3Tier_v1/Meshes/SM_WarMachine_Rigid.SM_WarMachine_Rigid</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/ElectromagneticMiner/LOD_3Tier_v1/BP_ElectromagneticMiner_3Tier.BP_ElectromagneticMiner_3Tier_C</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/ConstructionVehicle/LOD_3Tier_v1/BP_ConstructionVehicle_3Tier.BP_ConstructionVehicle_3Tier_C</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/SweeperSummon/LOD_3Tier_v1/Meshes/SM_Sweeper_Rigid.SM_Sweeper_Rigid</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/BiZhiMao/LOD_3Tier_v1/Meshes/SM_BiZhiMao_VAT.SM_BiZhiMao_VAT</t>
+  </si>
+  <si>
+    <t>/Game/GuLiStrike/Commander/Units/BiZhiMao/LOD_3Tier_v1/VAT/DA_BiZhiMao_VAT.DA_BiZhiMao_VAT</t>
   </si>
 </sst>
 </file>
@@ -1034,6 +1082,15 @@
       <c r="P1" t="s">
         <v>181</v>
       </c>
+      <c r="Q1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R1" t="s">
+        <v>189</v>
+      </c>
+      <c r="S1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -1084,6 +1141,15 @@
       <c r="P2" t="s">
         <v>41</v>
       </c>
+      <c r="Q2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -1132,6 +1198,15 @@
         <v>14</v>
       </c>
       <c r="P3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R3" t="s">
+        <v>14</v>
+      </c>
+      <c r="S3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1152,7 +1227,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1179,9 +1254,18 @@
         <v>141</v>
       </c>
       <c r="O4" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <v>0</v>
       </c>
     </row>
@@ -1202,7 +1286,7 @@
         <v>300.5</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1228,7 +1312,19 @@
       <c r="N5" t="s">
         <v>141</v>
       </c>
+      <c r="O5" t="s">
+        <v>68</v>
+      </c>
       <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>0</v>
       </c>
     </row>
@@ -1258,7 +1354,7 @@
         <v>125</v>
       </c>
       <c r="I6" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="J6">
         <v>0.6084579714416871</v>
@@ -1275,7 +1371,19 @@
       <c r="N6" t="s">
         <v>142</v>
       </c>
+      <c r="O6" t="s">
+        <v>68</v>
+      </c>
       <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
         <v>0</v>
       </c>
     </row>
@@ -1305,7 +1413,7 @@
         <v>129</v>
       </c>
       <c r="I7" t="s">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="J7">
         <v>0.6084579714416871</v>
@@ -1322,7 +1430,19 @@
       <c r="N7" t="s">
         <v>143</v>
       </c>
+      <c r="O7" t="s">
+        <v>68</v>
+      </c>
       <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
         <v>0</v>
       </c>
     </row>
@@ -1343,10 +1463,13 @@
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="G8">
         <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>68</v>
       </c>
       <c r="J8">
         <v>0.2</v>
@@ -1363,8 +1486,76 @@
       <c r="N8" t="s">
         <v>141</v>
       </c>
+      <c r="O8" t="s">
+        <v>68</v>
+      </c>
       <c r="P8" t="b">
         <v>1</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9">
+        <v>144</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J9">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
+        <v>194</v>
+      </c>
+      <c r="L9">
+        <v>18.4386</v>
+      </c>
+      <c r="M9">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="s">
+        <v>141</v>
+      </c>
+      <c r="O9" t="s">
+        <v>203</v>
+      </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>16.2975439453125</v>
       </c>
     </row>
   </sheetData>

--- a/data/Excel/GuLiStrikeCommander.xlsx
+++ b/data/Excel/GuLiStrikeCommander.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
   <si>
     <t>id</t>
   </si>
@@ -647,6 +647,81 @@
   </si>
   <si>
     <t>/Game/GuLiStrike/Commander/Units/BiZhiMao/LOD_3Tier_v1/VAT/DA_BiZhiMao_VAT.DA_BiZhiMao_VAT</t>
+  </si>
+  <si>
+    <t>ModelId</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1440</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.25</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>300.5</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>0.6084579714416871</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>18.4386</t>
+  </si>
+  <si>
+    <t>16.2975439453125</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +1102,10 @@
     <col customWidth="true" max="1" min="1" width="10"/>
     <col customWidth="true" max="2" min="2" width="22"/>
     <col customWidth="true" max="3" min="3" width="46"/>
-    <col customWidth="true" max="7" min="4" width="28"/>
-    <col customWidth="true" max="12" min="12" width="26"/>
-    <col customWidth="true" max="13" min="13" width="35"/>
-    <col customWidth="true" max="14" min="14" width="58"/>
+    <col customWidth="true" max="6" min="4" width="28"/>
+    <col customWidth="true" max="10" min="10" width="26"/>
+    <col customWidth="true" max="11" min="11" width="35"/>
+    <col customWidth="true" max="12" min="12" width="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1050,46 +1125,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="G1" t="s">
+        <v>119</v>
+      </c>
       <c r="H1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="J1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="K1" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="L1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M1" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="O1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="Q1" t="s">
-        <v>188</v>
-      </c>
-      <c r="R1" t="s">
-        <v>189</v>
-      </c>
-      <c r="S1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2">
@@ -1109,46 +1178,40 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" t="s">
-        <v>11</v>
-      </c>
       <c r="M2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="Q2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
         <v>9</v>
-      </c>
-      <c r="S2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1168,13 +1231,13 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>14</v>
@@ -1183,16 +1246,16 @@
         <v>13</v>
       </c>
       <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>13</v>
-      </c>
       <c r="N3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O3" t="s">
         <v>14</v>
@@ -1201,13 +1264,7 @@
         <v>14</v>
       </c>
       <c r="Q3" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1226,47 +1283,41 @@
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
         <v>68</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="I4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
         <v>184</v>
       </c>
-      <c r="L4" s="8">
+      <c r="J4" s="8">
         <v>6.25</v>
       </c>
-      <c r="M4" s="8">
+      <c r="K4" s="8">
         <v>0.5</v>
       </c>
-      <c r="N4" t="s">
+      <c r="L4" t="s">
         <v>141</v>
       </c>
-      <c r="O4" t="s">
-        <v>197</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1001</v>
       </c>
     </row>
     <row r="5">
@@ -1285,47 +1336,41 @@
       <c r="E5">
         <v>300.5</v>
       </c>
-      <c r="F5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
         <v>68</v>
       </c>
+      <c r="H5">
+        <v>0.2</v>
+      </c>
       <c r="I5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5">
-        <v>0.2</v>
-      </c>
-      <c r="K5" t="s">
         <v>146</v>
       </c>
-      <c r="L5" s="8">
+      <c r="J5" s="8">
         <v>12.5</v>
       </c>
-      <c r="M5" s="8">
+      <c r="K5" s="8">
         <v>2.5</v>
       </c>
-      <c r="N5" t="s">
+      <c r="L5" t="s">
         <v>141</v>
       </c>
-      <c r="O5" t="s">
-        <v>68</v>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1002</v>
       </c>
     </row>
     <row r="6">
@@ -1344,47 +1389,41 @@
       <c r="E6">
         <v>1000</v>
       </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>125</v>
       </c>
+      <c r="H6">
+        <v>0.6084579714416871</v>
+      </c>
       <c r="I6" t="s">
-        <v>199</v>
-      </c>
-      <c r="J6">
-        <v>0.6084579714416871</v>
-      </c>
-      <c r="K6" t="s">
         <v>133</v>
       </c>
-      <c r="L6" s="8">
+      <c r="J6" s="8">
         <v>3.6</v>
       </c>
-      <c r="M6" s="8">
+      <c r="K6" s="8">
         <v>1</v>
       </c>
-      <c r="N6" t="s">
+      <c r="L6" t="s">
         <v>142</v>
       </c>
-      <c r="O6" t="s">
-        <v>68</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1003</v>
       </c>
     </row>
     <row r="7">
@@ -1403,47 +1442,41 @@
       <c r="E7">
         <v>1000</v>
       </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>129</v>
       </c>
+      <c r="H7">
+        <v>0.6084579714416871</v>
+      </c>
       <c r="I7" t="s">
-        <v>200</v>
-      </c>
-      <c r="J7">
-        <v>0.6084579714416871</v>
-      </c>
-      <c r="K7" t="s">
         <v>134</v>
       </c>
-      <c r="L7" s="8">
+      <c r="J7" s="8">
         <v>3.6</v>
       </c>
-      <c r="M7" s="8">
+      <c r="K7" s="8">
         <v>1</v>
       </c>
-      <c r="N7" t="s">
+      <c r="L7" t="s">
         <v>143</v>
       </c>
-      <c r="O7" t="s">
-        <v>68</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1004</v>
       </c>
     </row>
     <row r="8">
@@ -1462,44 +1495,41 @@
       <c r="E8">
         <v>100</v>
       </c>
-      <c r="F8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8">
+        <v>0.2</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="J8">
-        <v>0.2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>131</v>
-      </c>
-      <c r="L8">
         <v>3.1</v>
       </c>
-      <c r="M8">
+      <c r="K8">
         <v>0.5</v>
       </c>
-      <c r="N8" t="s">
+      <c r="L8" t="s">
         <v>141</v>
       </c>
-      <c r="O8" t="s">
-        <v>68</v>
-      </c>
-      <c r="P8" t="b">
+      <c r="M8" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1005</v>
       </c>
     </row>
     <row r="9">
@@ -1518,44 +1548,41 @@
       <c r="E9">
         <v>1000</v>
       </c>
-      <c r="F9" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>194</v>
-      </c>
-      <c r="L9">
         <v>18.4386</v>
       </c>
-      <c r="M9">
+      <c r="K9">
         <v>0.5</v>
       </c>
-      <c r="N9" t="s">
+      <c r="L9" t="s">
         <v>141</v>
       </c>
-      <c r="O9" t="s">
-        <v>203</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
         <v>1</v>
       </c>
-      <c r="R9">
+      <c r="O9">
         <v>1</v>
       </c>
-      <c r="S9">
+      <c r="P9">
         <v>16.2975439453125</v>
+      </c>
+      <c r="Q9">
+        <v>1006</v>
       </c>
     </row>
   </sheetData>
